--- a/output/problem3_results.xlsx
+++ b/output/problem3_results.xlsx
@@ -608,40 +608,40 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G2" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0.584</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I2" s="2" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" s="2" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>0.833</v>
-      </c>
       <c r="M2" s="2" t="n">
-        <v>0.667</v>
+        <v>0.312</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>1</v>
@@ -650,29 +650,29 @@
         <v>1</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>0.515</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>1</v>
+        <v>0.655</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>89.76000000000001</v>
+        <v>35.59</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>77.97</v>
+        <v>64.89</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>73.88</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>86.62</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>81.54000000000001</v>
+        <v>59.12</v>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>优秀</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="X2" s="2" t="n">
@@ -691,40 +691,40 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.904</v>
+        <v>0.367</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1</v>
+        <v>0.824</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.694</v>
+        <v>0.917</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0.625</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.167</v>
+        <v>1</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.556</v>
+        <v>1</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1</v>
+        <v>0.841</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.315</v>
+        <v>0.408</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.556</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.312</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>1</v>
@@ -736,26 +736,26 @@
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>1</v>
+        <v>0.49</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>82.98999999999999</v>
+        <v>43.2</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>50.85</v>
+        <v>62.73</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>66.25</v>
+        <v>80.69</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>89.65000000000001</v>
+        <v>72.52</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>66.11</v>
+        <v>60.97</v>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>良好</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="X3" s="2" t="n">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="H4" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.694</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0.484</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>0.833</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.905</v>
+        <v>0.977</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.284</v>
+        <v>0.398</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.667</v>
+        <v>0.312</v>
       </c>
       <c r="N4" s="2" t="n">
         <v>1</v>
@@ -816,29 +816,29 @@
         <v>1</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0.876</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>1</v>
+        <v>0.576</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>83.98999999999999</v>
+        <v>38.02</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>77.70999999999999</v>
+        <v>61.64</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>80.40000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>88.83</v>
+        <v>73.47</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>81.01000000000001</v>
+        <v>59.04</v>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>优秀</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="X4" s="2" t="n">
@@ -1311,7 +1311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1368,29 +1368,29 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>u31</t>
+          <t>u14</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>有效公式密度</t>
+          <t>逻辑断层条数</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.153</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>指标得分低于0.5（U3维度）</t>
+          <t>指标得分低于0.5（U1维度）</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>将核心模型用公式化表达并编号，避免大段文字描述代替公式</t>
+          <t>检查并补全跳过的推导步骤，消除“直接给出结果”的断层</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.403</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="3">
@@ -1401,16 +1401,16 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>u32</t>
+          <t>u31</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>公式标注规范率</t>
+          <t>有效公式密度</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.222</v>
+        <v>0.187</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
@@ -1419,11 +1419,11 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>为关键公式添加(1)(2)…编号，并补充符号说明表</t>
+          <t>将核心模型用公式化表达并编号，避免大段文字描述代替公式</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.472</v>
+        <v>0.437</v>
       </c>
     </row>
     <row r="4">
@@ -1434,128 +1434,128 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>u13</t>
+          <t>u34</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>论证闭环完整率</t>
+          <t>符号统一度</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.833</v>
+        <v>0.312</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>检测发现（全文）：已有收敛性分析，建议补充灵敏度/误差分析以强化稳定性论证</t>
+          <t>指标得分低于0.5（U3维度）</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>增加模型检验环节：误差分析、灵敏度分析、收敛性验证与结果吻合性说明</t>
+          <t>统一并集中定义全文符号，增加符号说明/变量定义</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.873</v>
+        <v>0.492</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>3-2.pdf</t>
+          <t>3-1.pdf</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>u22</t>
+          <t>u32</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>假设适配度</t>
+          <t>公式标注规范率</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.167</v>
+        <v>0.375</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>指标得分低于0.5（U2维度）</t>
+          <t>指标得分低于0.5（U3维度）</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>在建模前显式列出基本假设与前提条件，并说明其合理性</t>
+          <t>为关键公式添加(1)(2)…编号，并补充符号说明表</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.417</v>
+        <v>0.555</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>3-2.pdf</t>
+          <t>3-1.pdf</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>u32</t>
+          <t>u11</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>公式标注规范率</t>
+          <t>逻辑连接词密度</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.315</v>
+        <v>0.397</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>指标得分低于0.5（U3维度）</t>
+          <t>指标得分低于0.5（U1维度）</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>为关键公式添加(1)(2)…编号，并补充符号说明表</t>
+          <t>在问题分析、模型推导与结论处补充“因此、综上、进而、由此可得”等逻辑连接词，增强论证衔接</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.495</v>
+        <v>0.577</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>3-2.pdf</t>
+          <t>3-1.pdf</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>u34</t>
+          <t>u13</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>符号统一度</t>
+          <t>论证闭环完整率</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.333</v>
+        <v>0.743</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>指标得分低于0.5（U3维度）</t>
+          <t>检测发现（全文）：已有收敛性分析，建议补充灵敏度/误差分析以强化稳定性论证</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>统一并集中定义全文符号，增加符号说明/变量定义</t>
+          <t>增加模型检验环节：误差分析、灵敏度分析、收敛性验证与结果吻合性说明</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.513</v>
+        <v>0.783</v>
       </c>
     </row>
     <row r="8">
@@ -1566,49 +1566,49 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>u13</t>
+          <t>u14</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>论证闭环完整率</t>
+          <t>逻辑断层条数</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.694</v>
+        <v>0</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>检测发现（全文）：已有收敛性分析，建议补充灵敏度/误差分析以强化稳定性论证</t>
+          <t>指标得分低于0.5（U1维度）</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>增加模型检验环节：误差分析、灵敏度分析、收敛性验证与结果吻合性说明</t>
+          <t>检查并补全跳过的推导步骤，消除“直接给出结果”的断层</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.794</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>3-3.pdf</t>
+          <t>3-2.pdf</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>u32</t>
+          <t>u34</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>公式标注规范率</t>
+          <t>符号统一度</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.284</v>
+        <v>0.312</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
@@ -1617,77 +1617,308 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>为关键公式添加(1)(2)…编号，并补充符号说明表</t>
+          <t>统一并集中定义全文符号，增加符号说明/变量定义</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.534</v>
+        <v>0.492</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>3-3.pdf</t>
+          <t>3-2.pdf</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>u22</t>
+          <t>u11</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>假设适配度</t>
+          <t>逻辑连接词密度</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.484</v>
+        <v>0.367</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>指标得分低于0.5（U2维度）</t>
+          <t>指标得分低于0.5（U1维度）</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>在建模前显式列出基本假设与前提条件，并说明其合理性</t>
+          <t>在问题分析、模型推导与结论处补充“因此、综上、进而、由此可得”等逻辑连接词，增强论证衔接</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.664</v>
+        <v>0.547</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>3-2.pdf</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>u32</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>公式标注规范率</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>指标得分低于0.5（U3维度）</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>为关键公式添加(1)(2)…编号，并补充符号说明表</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>0.588</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>3-2.pdf</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>u44</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>文本冗余度</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>指标得分低于0.5（U4维度）</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>删减重复赘述，压缩冗余表达，提高信息密度</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>3-2.pdf</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>u13</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>论证闭环完整率</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>检测发现（全文）：已有收敛性分析，建议补充灵敏度/误差分析以强化稳定性论证</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>增加模型检验环节：误差分析、灵敏度分析、收敛性验证与结果吻合性说明</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>3-3.pdf</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>u14</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>逻辑断层条数</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>指标得分低于0.5（U1维度）</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>检查并补全跳过的推导步骤，消除“直接给出结果”的断层</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>3-3.pdf</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>u34</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>符号统一度</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>指标得分低于0.5（U3维度）</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>统一并集中定义全文符号，增加符号说明/变量定义</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>0.492</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>3-3.pdf</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>u11</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>逻辑连接词密度</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>指标得分低于0.5（U1维度）</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>在问题分析、模型推导与结论处补充“因此、综上、进而、由此可得”等逻辑连接词，增强论证衔接</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>0.546</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>3-3.pdf</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>u32</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>公式标注规范率</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>指标得分低于0.5（U3维度）</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>为关键公式添加(1)(2)…编号，并补充符号说明表</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>0.578</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>3-3.pdf</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>u13</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>论证闭环完整率</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
-        <v>0.694</v>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="D18" s="2" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>检测发现（全文）：已有收敛性分析，建议补充灵敏度/误差分析以强化稳定性论证</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>增加模型检验环节：误差分析、灵敏度分析、收敛性验证与结果吻合性说明</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n">
-        <v>0.794</v>
+      <c r="G18" s="2" t="n">
+        <v>0.828</v>
       </c>
     </row>
   </sheetData>
@@ -1751,23 +1982,23 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>81.54000000000001</v>
+        <v>59.12</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>优秀</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>82.81</v>
+        <v>61.39</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>优秀</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1.27</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="3">
@@ -1777,23 +2008,23 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>66.11</v>
+        <v>60.97</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>良好</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>70.84</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>良好</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>4.73</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="4">
@@ -1803,23 +2034,23 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>81.01000000000001</v>
+        <v>59.04</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>优秀</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>84.56999999999999</v>
+        <v>61.82</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>优秀</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3.56</v>
+        <v>2.78</v>
       </c>
     </row>
   </sheetData>
@@ -1833,7 +2064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1876,10 +2107,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.25</v>
+        <v>0.18</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.97</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="3">
@@ -1890,14 +2121,14 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>有效公式密度</t>
+          <t>逻辑连接词密度</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.25</v>
+        <v>0.18</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.3</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="4">
@@ -1908,68 +2139,68 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>论证闭环完整率</t>
+          <t>逻辑断层条数</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.04</v>
+        <v>0.25</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>3-2.pdf</t>
+          <t>3-1.pdf</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>假设适配度</t>
+          <t>符号统一度</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.25</v>
+        <v>0.179</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2.19</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>3-2.pdf</t>
+          <t>3-1.pdf</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>论证闭环完整率</t>
+          <t>有效公式密度</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1.61</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>3-2.pdf</t>
+          <t>3-1.pdf</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>公式标注规范率</t>
+          <t>论证闭环完整率</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.18</v>
+        <v>0.04</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1980,68 +2211,194 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>符号统一度</t>
+          <t>论证闭环完整率</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.18</v>
+        <v>0.033</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.29</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>3-3.pdf</t>
+          <t>3-2.pdf</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>论证闭环完整率</t>
+          <t>公式标注规范率</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1.61</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>3-3.pdf</t>
+          <t>3-2.pdf</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>假设适配度</t>
+          <t>逻辑连接词密度</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v>0.18</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1.17</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>3-3.pdf</t>
+          <t>3-2.pdf</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>公式标注规范率</t>
+          <t>逻辑断层条数</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v>0.25</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.77</v>
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>3-2.pdf</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>符号统一度</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>3-2.pdf</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>文本冗余度</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>3-3.pdf</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>论证闭环完整率</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>3-3.pdf</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>公式标注规范率</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>3-3.pdf</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>逻辑连接词密度</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>3-3.pdf</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>逻辑断层条数</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>3-3.pdf</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>符号统一度</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.31</v>
       </c>
     </row>
   </sheetData>

--- a/output/problem3_results.xlsx
+++ b/output/problem3_results.xlsx
@@ -659,7 +659,7 @@
         <v>35.59</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>64.89</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="T2" s="2" t="n">
         <v>74.34999999999999</v>
@@ -668,7 +668,7 @@
         <v>74.51000000000001</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>59.12</v>
+        <v>59.79</v>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>43.2</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>62.73</v>
+        <v>66.13</v>
       </c>
       <c r="T3" s="2" t="n">
         <v>80.69</v>
@@ -751,7 +751,7 @@
         <v>72.52</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>60.97</v>
+        <v>62.56</v>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>59.12</v>
+        <v>59.79</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>61.39</v>
+        <v>62.06</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>60.97</v>
+        <v>62.56</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -2016,11 +2016,11 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>64.43000000000001</v>
+        <v>66.02</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>中等</t>
+          <t>良好</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">

--- a/output/problem3_results.xlsx
+++ b/output/problem3_results.xlsx
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="X2" s="2" t="n">
-        <v>0.285</v>
+        <v>0.316</v>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.185</v>
+        <v>0.21</v>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.18</v>
+        <v>0.183</v>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -873,13 +873,16 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -920,45 +923,60 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>逻辑异常度</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>术语偏离度</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>AI辅助指数</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>辅助程度</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>句长CV</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>段落CV</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>套话密度‰</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>连接词密度‰</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>术语丰富度</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>数字密度‰</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>重复率</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>图表密度‰</t>
         </is>
@@ -989,32 +1007,41 @@
         <v>0.429</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
+        <v>0.748</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="L2" s="2" t="n">
         <v>0.705</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="M2" s="2" t="n">
         <v>0.673</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="N2" s="2" t="n">
         <v>1.898</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="O2" s="2" t="n">
         <v>0.925</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="P2" s="2" t="n">
+        <v>0.4912</v>
+      </c>
+      <c r="Q2" s="2" t="n">
         <v>47.649</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="R2" s="2" t="n">
         <v>0.0515</v>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="S2" s="2" t="n">
         <v>2.434</v>
       </c>
     </row>
@@ -1043,32 +1070,41 @@
         <v>0.845</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
+        <v>0.546</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="L3" s="2" t="n">
         <v>0.708</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="M3" s="2" t="n">
         <v>0.6850000000000001</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="N3" s="2" t="n">
         <v>0.371</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="O3" s="2" t="n">
         <v>0.632</v>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="P3" s="2" t="n">
+        <v>0.4776</v>
+      </c>
+      <c r="Q3" s="2" t="n">
         <v>59.365</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="R3" s="2" t="n">
         <v>0.1014</v>
       </c>
-      <c r="P3" s="2" t="n">
+      <c r="S3" s="2" t="n">
         <v>1.152</v>
       </c>
     </row>
@@ -1097,32 +1133,41 @@
         <v>0.7</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+        <v>0.202</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="L4" s="2" t="n">
         <v>0.695</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="M4" s="2" t="n">
         <v>0.642</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="N4" s="2" t="n">
         <v>0.516</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="O4" s="2" t="n">
         <v>0.709</v>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="P4" s="2" t="n">
+        <v>0.4504</v>
+      </c>
+      <c r="Q4" s="2" t="n">
         <v>60.666</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="R4" s="2" t="n">
         <v>0.08400000000000001</v>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="S4" s="2" t="n">
         <v>0.86</v>
       </c>
     </row>

--- a/output/problem3_results.xlsx
+++ b/output/problem3_results.xlsx
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="X2" s="2" t="n">
-        <v>0.316</v>
+        <v>0.361</v>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.21</v>
+        <v>0.276</v>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.183</v>
+        <v>0.256</v>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
@@ -1007,13 +1007,13 @@
         <v>0.429</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.748</v>
+        <v>1</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.128</v>
+        <v>0.267</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.316</v>
+        <v>0.361</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -1070,13 +1070,13 @@
         <v>0.845</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.546</v>
+        <v>1</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.032</v>
+        <v>0.166</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.21</v>
+        <v>0.276</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>0.7</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.202</v>
+        <v>1</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.16</v>
+        <v>0.033</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.183</v>
+        <v>0.256</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>

--- a/output/problem3_results.xlsx
+++ b/output/problem3_results.xlsx
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="X2" s="2" t="n">
-        <v>0.361</v>
+        <v>0.17</v>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
@@ -759,11 +759,11 @@
         </is>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.276</v>
+        <v>0.45</v>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
     </row>
@@ -842,11 +842,11 @@
         </is>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.256</v>
+        <v>0.729</v>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -873,16 +873,10 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -893,92 +887,62 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>句长均匀度</t>
+          <t>句子重复度</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>句式变化性</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>段落均匀度</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>套话密度</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>连接词密度</t>
+          <t>逻辑异常度</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>低具体性</t>
+          <t>术语偏离度</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>重复率</t>
+          <t>AI辅助指数</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>逻辑异常度</t>
+          <t>辅助程度</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>术语偏离度</t>
+          <t>句首重复率</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>AI辅助指数</t>
+          <t>句式变化性(原始)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>辅助程度</t>
+          <t>段落均匀度(原始)</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>句长CV</t>
+          <t>逻辑连接词密度</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>段落CV</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>套话密度‰</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>连接词密度‰</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
           <t>术语丰富度</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>数字密度‰</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>重复率</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>图表密度‰</t>
         </is>
       </c>
     </row>
@@ -989,60 +953,42 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0</v>
+        <v>0.104</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.949</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.308</v>
+        <v>0.256</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>1</v>
+        <v>0.17</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.267</v>
+        <v>0.0163</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0.32</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.705</v>
+        <v>18.453</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.673</v>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>1.898</v>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="P2" s="2" t="n">
-        <v>0.4912</v>
-      </c>
-      <c r="Q2" s="2" t="n">
-        <v>47.649</v>
-      </c>
-      <c r="R2" s="2" t="n">
-        <v>0.0515</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>2.434</v>
+        <v>0.9031</v>
       </c>
     </row>
     <row r="3">
@@ -1055,57 +1001,39 @@
         <v>0</v>
       </c>
       <c r="C3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0.211</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>1</v>
+        <v>0.45</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.166</v>
+        <v>0.0135</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.276</v>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
+        <v>0.581</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0.847</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.708</v>
+        <v>16.985</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>0.371</v>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>0.632</v>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>0.4776</v>
-      </c>
-      <c r="Q3" s="2" t="n">
-        <v>59.365</v>
-      </c>
-      <c r="R3" s="2" t="n">
-        <v>0.1014</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>1.152</v>
+        <v>0.8542</v>
       </c>
     </row>
     <row r="4">
@@ -1115,60 +1043,42 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.258</v>
+        <v>0.751</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.236</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0</v>
+        <v>0.412</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>1</v>
+        <v>0.729</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.033</v>
+        <v>0.0401</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.256</v>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0.716</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.695</v>
+        <v>22.728</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.642</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>0.516</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>0.709</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>0.4504</v>
-      </c>
-      <c r="Q4" s="2" t="n">
-        <v>60.666</v>
-      </c>
-      <c r="R4" s="2" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>0.86</v>
+        <v>0.7942</v>
       </c>
     </row>
   </sheetData>

--- a/output/problem3_results.xlsx
+++ b/output/problem3_results.xlsx
@@ -1266,7 +1266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>指标得分低于0.5（U1维度）</t>
+          <t>指标得分低于0.6（U1维度）</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="3">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>指标得分低于0.5（U3维度）</t>
+          <t>指标得分低于0.6（U3维度）</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.437</v>
+        <v>0.487</v>
       </c>
     </row>
     <row r="4">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>指标得分低于0.5（U3维度）</t>
+          <t>指标得分低于0.6（U3维度）</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.492</v>
+        <v>0.532</v>
       </c>
     </row>
     <row r="5">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>指标得分低于0.5（U3维度）</t>
+          <t>指标得分低于0.6（U3维度）</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.555</v>
+        <v>0.595</v>
       </c>
     </row>
     <row r="6">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>指标得分低于0.5（U1维度）</t>
+          <t>指标得分低于0.6（U1维度）</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.577</v>
+        <v>0.617</v>
       </c>
     </row>
     <row r="7">
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.783</v>
+        <v>0.793</v>
       </c>
     </row>
     <row r="8">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>指标得分低于0.5（U1维度）</t>
+          <t>指标得分低于0.6（U1维度）</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="9">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>指标得分低于0.5（U3维度）</t>
+          <t>指标得分低于0.6（U3维度）</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.492</v>
+        <v>0.532</v>
       </c>
     </row>
     <row r="10">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>指标得分低于0.5（U1维度）</t>
+          <t>指标得分低于0.6（U1维度）</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.547</v>
+        <v>0.587</v>
       </c>
     </row>
     <row r="11">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>指标得分低于0.5（U3维度）</t>
+          <t>指标得分低于0.6（U3维度）</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.588</v>
+        <v>0.628</v>
       </c>
     </row>
     <row r="12">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>指标得分低于0.5（U4维度）</t>
+          <t>指标得分低于0.6（U4维度）</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="13">
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.95</v>
+        <v>0.967</v>
       </c>
     </row>
     <row r="14">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>指标得分低于0.5（U1维度）</t>
+          <t>指标得分低于0.6（U1维度）</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="15">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>指标得分低于0.5（U3维度）</t>
+          <t>指标得分低于0.6（U3维度）</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.492</v>
+        <v>0.532</v>
       </c>
     </row>
     <row r="16">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>指标得分低于0.5（U1维度）</t>
+          <t>指标得分低于0.6（U1维度）</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.546</v>
+        <v>0.586</v>
       </c>
     </row>
     <row r="17">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>指标得分低于0.5（U3维度）</t>
+          <t>指标得分低于0.6（U3维度）</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.578</v>
+        <v>0.618</v>
       </c>
     </row>
     <row r="18">
@@ -1851,29 +1851,95 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
+          <t>u44</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>文本冗余度</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>指标得分低于0.6（U4维度）</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>删减重复赘述，压缩冗余表达，提高信息密度</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>0.696</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>3-3.pdf</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>u21</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>模型匹配度</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>指标得分低于0.6（U2维度）</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>明确说明所选模型与问题类型的匹配性（如优化/预测/评价问题对应的方法）</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>0.712</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>3-3.pdf</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>u13</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>论证闭环完整率</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D20" s="2" t="n">
         <v>0.788</v>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>检测发现（全文）：已有收敛性分析，建议补充灵敏度/误差分析以强化稳定性论证</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>增加模型检验环节：误差分析、灵敏度分析、收敛性验证与结果吻合性说明</t>
         </is>
       </c>
-      <c r="G18" s="2" t="n">
-        <v>0.828</v>
+      <c r="G20" s="2" t="n">
+        <v>0.838</v>
       </c>
     </row>
   </sheetData>
@@ -1945,7 +2011,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>62.06</v>
+        <v>62.34</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -1953,7 +2019,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="3">
@@ -1971,7 +2037,7 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>66.02</v>
+        <v>66.67</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -1979,7 +2045,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3.46</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="4">
@@ -1997,15 +2063,15 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>61.82</v>
+        <v>71.89</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>中等</t>
+          <t>良好</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2.78</v>
+        <v>12.85</v>
       </c>
     </row>
   </sheetData>
@@ -2019,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2062,7 +2128,7 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0.87</v>
@@ -2080,10 +2146,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.54</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="4">
@@ -2094,14 +2160,14 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>逻辑断层条数</t>
+          <t>符号统一度</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="5">
@@ -2112,14 +2178,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>符号统一度</t>
+          <t>逻辑断层条数</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.179</v>
+        <v>0.3</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.31</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="6">
@@ -2134,10 +2200,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="7">
@@ -2152,7 +2218,7 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0</v>
@@ -2170,10 +2236,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.033</v>
+        <v>0.05</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1.42</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="9">
@@ -2188,7 +2254,7 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0.7</v>
@@ -2206,10 +2272,10 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.54</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="11">
@@ -2220,14 +2286,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>逻辑断层条数</t>
+          <t>符号统一度</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="12">
@@ -2238,14 +2304,14 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>符号统一度</t>
+          <t>逻辑断层条数</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.179</v>
+        <v>0.3</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.31</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="13">
@@ -2260,10 +2326,10 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="14">
@@ -2274,14 +2340,14 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>论证闭环完整率</t>
+          <t>模型匹配度</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.82</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="15">
@@ -2292,14 +2358,14 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>公式标注规范率</t>
+          <t>论证闭环完整率</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.75</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="16">
@@ -2310,14 +2376,14 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>逻辑连接词密度</t>
+          <t>公式标注规范率</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.54</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="17">
@@ -2328,14 +2394,14 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>逻辑断层条数</t>
+          <t>逻辑连接词密度</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.37</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="18">
@@ -2350,10 +2416,46 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0.179</v>
+        <v>0.22</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.31</v>
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>3-3.pdf</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>逻辑断层条数</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>3-3.pdf</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>文本冗余度</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>
